--- a/Web/TestCasesWeb/Facturacion.xlsx
+++ b/Web/TestCasesWeb/Facturacion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA4D029-17F1-4D65-810B-2C7C3CAD3A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34F056C-8295-4BCA-A40A-41A2141ABF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
     <t>Num</t>
   </si>
@@ -49,9 +49,6 @@
     <t>pte</t>
   </si>
   <si>
-    <t>Invoice page home</t>
-  </si>
-  <si>
     <t>INV001</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
   </si>
   <si>
     <t>INV004</t>
-  </si>
-  <si>
-    <t>1. Invoice page home is correctly.</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks "Facturación"
@@ -80,13 +74,208 @@
   </si>
   <si>
     <t>1. The invoice is correctly.</t>
+  </si>
+  <si>
+    <t>1. Invoice page is correctly.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Invoicing page</t>
+  </si>
+  <si>
+    <t>Invoicing: Invoices</t>
+  </si>
+  <si>
+    <t>Invoicing: Configuration, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Invoicing: Configuration, all parameters</t>
+  </si>
+  <si>
+    <t>1. The configuration is saved.</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>1. The users selects: Configuration
+2. Fills the mandatory fields
+3. Clicks "Guardar configuración"</t>
+  </si>
+  <si>
+    <t>1. The users selects: Configuration
+2. Fills the all fields
+3. Clicks "Guardar configuración"</t>
+  </si>
+  <si>
+    <t>Invoicing: Configuration, cancel</t>
+  </si>
+  <si>
+    <t>1. The users selects: Configuration
+2. Fills the all fields
+3. Clicks "cancelar"</t>
+  </si>
+  <si>
+    <t>1. The configuration is not saved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/04/26: BLOQUEANTE ,No se puede rellenar nada. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">16/04/26: BLOQUEANTE ,No se puede rellenar nada. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16/04/26: No están marcados los campos obligatorios</t>
+    </r>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+2. Clicks "Crear primera serie"
+2. Fills the all fields
+3. Clicks "Guardar configuración"</t>
+  </si>
+  <si>
+    <t>Invoicing: create first serie</t>
+  </si>
+  <si>
+    <t>Invoicing: create another serie</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+2. Clicks "Nueva serie"
+2. Fills the all fields
+3. Clicks "Guardar configuración"</t>
+  </si>
+  <si>
+    <t>1. The serie is created</t>
+  </si>
+  <si>
+    <t>Invoicing: modify serie</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+2. Clicks a serie created
+2. Modify fields
+3. Clicks "Guardar "</t>
+  </si>
+  <si>
+    <t>1. The serie is modified</t>
+  </si>
+  <si>
+    <t>Invoicing: Series, activate</t>
+  </si>
+  <si>
+    <t>Invoicing: Series, deactivate</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+e. Clicks "active" a serie</t>
+  </si>
+  <si>
+    <t>1. The serie is activated</t>
+  </si>
+  <si>
+    <t>1. The serie is deactivated</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+e. Clicks "deactive" a serie</t>
+  </si>
+  <si>
+    <t>No hay facturas</t>
+  </si>
+  <si>
+    <t>INV005</t>
+  </si>
+  <si>
+    <t>INV006</t>
+  </si>
+  <si>
+    <t>INV007</t>
+  </si>
+  <si>
+    <t>INV008</t>
+  </si>
+  <si>
+    <t>INV009</t>
+  </si>
+  <si>
+    <t>INV010</t>
+  </si>
+  <si>
+    <t>INV011</t>
+  </si>
+  <si>
+    <t>Invoicing: delete serie</t>
+  </si>
+  <si>
+    <t>Invoicing: delete serie,cancel</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+2. Clicks the icon garbage
+3. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>1. The serie is deleted</t>
+  </si>
+  <si>
+    <t>1. The user selects: Series
+2. Clicks the icon garbage
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The operation is cancelled</t>
+  </si>
+  <si>
+    <t>1. The serie is not deleted</t>
+  </si>
+  <si>
+    <t>16/04/26: No funciona el botón eliminar</t>
+  </si>
+  <si>
+    <t>INV012</t>
+  </si>
+  <si>
+    <t>INV013</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +305,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -157,7 +353,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -183,12 +379,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -523,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -564,20 +794,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="8" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H2" s="7"/>
     </row>
@@ -586,16 +816,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="8" t="s">
@@ -603,52 +833,296 @@
       </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
+      <formula>NOT(ISERROR(SEARCH("KO",G14)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("OK",G14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Web/TestCasesWeb/Facturacion.xlsx
+++ b/Web/TestCasesWeb/Facturacion.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34F056C-8295-4BCA-A40A-41A2141ABF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -387,38 +387,7 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1097,32 +1066,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G13">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G2:G14">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G14">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G14)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G14)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G14)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Web/TestCasesWeb/Facturacion.xlsx
+++ b/Web/TestCasesWeb/Facturacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34F056C-8295-4BCA-A40A-41A2141ABF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEE5F29-5445-46AD-A192-B47B87A8BEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>Num</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>pte</t>
   </si>
   <si>
     <t>INV001</t>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>INV013</t>
+  </si>
+  <si>
+    <t>No se pueder generar facturas, con lo q no pueden verse</t>
   </si>
 </sst>
 </file>
@@ -371,9 +371,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -381,6 +378,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -763,67 +763,69 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="6"/>
+      <c r="G3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -831,23 +833,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>30</v>
+      <c r="H5" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -855,22 +857,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -879,22 +881,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -903,22 +905,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="H8" s="4"/>
     </row>
@@ -927,22 +929,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -951,25 +953,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -977,22 +979,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -1001,22 +1003,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>18</v>
+        <v>43</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -1025,22 +1027,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -1049,19 +1051,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="8" t="s">
-        <v>32</v>
+      <c r="G14" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Web/TestCasesWeb/Facturacion.xlsx
+++ b/Web/TestCasesWeb/Facturacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFEE5F29-5445-46AD-A192-B47B87A8BEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EF89CD-F338-478B-8B19-3F31ECE6F5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
   <si>
     <t>Num</t>
   </si>
@@ -210,9 +210,6 @@
 e. Clicks "deactive" a serie</t>
   </si>
   <si>
-    <t>No hay facturas</t>
-  </si>
-  <si>
     <t>INV005</t>
   </si>
   <si>
@@ -256,9 +253,6 @@
     <t>1. The operation is cancelled</t>
   </si>
   <si>
-    <t>1. The serie is not deleted</t>
-  </si>
-  <si>
     <t>16/04/26: No funciona el botón eliminar</t>
   </si>
   <si>
@@ -268,7 +262,10 @@
     <t>INV013</t>
   </si>
   <si>
-    <t>No se pueder generar facturas, con lo q no pueden verse</t>
+    <t>BLOQUEANTE: No hay facturas</t>
+  </si>
+  <si>
+    <t>BLOQUEANTE: No se pueder generar facturas, con lo q no pueden verse</t>
   </si>
 </sst>
 </file>
@@ -798,10 +795,10 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -857,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
@@ -881,7 +878,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>33</v>
@@ -905,7 +902,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>34</v>
@@ -929,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>37</v>
@@ -953,25 +950,23 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -979,19 +974,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>17</v>
@@ -1003,7 +998,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>40</v>
@@ -1027,7 +1022,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>41</v>
@@ -1051,7 +1046,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>19</v>
@@ -1060,10 +1055,10 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>46</v>
+        <v>23</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
